--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T10:34:48+00:00</t>
+    <t>2026-03-06T12:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:21:15+00:00</t>
+    <t>2026-03-09T10:11:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:11:56+00:00</t>
+    <t>2026-03-09T10:54:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:54:50+00:00</t>
+    <t>2026-03-09T16:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T16:16:18+00:00</t>
+    <t>2026-03-16T17:28:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T17:28:45+00:00</t>
+    <t>2026-06-10T07:22:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T07:22:25+00:00</t>
+    <t>2026-06-11T14:21:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
+++ b/448-contenu-fhir---ajout-du-projet-de-vie/ig/CodeSystem-tddui-task-input-moyen-ressource.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:21:35+00:00</t>
+    <t>2026-06-11T15:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
